--- a/tests/fixtures/census_tabs15-65_trimmed.xlsx
+++ b/tests/fixtures/census_tabs15-65_trimmed.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Alaska" sheetId="58" r:id="rId2"/>
     <sheet name="Connecticut" sheetId="63" r:id="rId7"/>
+    <sheet name="Hawaii" sheetId="68" r:id="rId12"/>
     <sheet name="Virginia" sheetId="103" r:id="rId47"/>
     <sheet name="West Virginia" sheetId="105" r:id="rId49"/>
   </sheets>
@@ -4333,6 +4334,1272 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6855753-E64C-430E-9E9E-16477286A380}">
+  <dimension ref="A1:I60"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" style="3" customWidth="1"/>
+    <col min="2" max="9" width="14.1796875" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="77" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50" x14ac:dyDescent="0.25">
+      <c r="A4" s="76"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+    </row>
+    <row r="5" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+      <c r="A6" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="136">
+        <v>1108229</v>
+      </c>
+      <c r="C7" s="20">
+        <v>369616</v>
+      </c>
+      <c r="D7" s="20">
+        <v>27195</v>
+      </c>
+      <c r="E7" s="20">
+        <v>5099</v>
+      </c>
+      <c r="F7" s="20">
+        <v>685236</v>
+      </c>
+      <c r="G7" s="21">
+        <v>21083</v>
+      </c>
+      <c r="H7" s="22">
+        <v>81390</v>
+      </c>
+      <c r="I7" s="22">
+        <v>347644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="136">
+        <v>1108229</v>
+      </c>
+      <c r="C8" s="20">
+        <v>370270</v>
+      </c>
+      <c r="D8" s="20">
+        <v>26669</v>
+      </c>
+      <c r="E8" s="20">
+        <v>5596</v>
+      </c>
+      <c r="F8" s="20">
+        <v>686391</v>
+      </c>
+      <c r="G8" s="21">
+        <v>19303</v>
+      </c>
+      <c r="H8" s="22">
+        <v>78742</v>
+      </c>
+      <c r="I8" s="22">
+        <v>347804</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="136">
+        <v>964691</v>
+      </c>
+      <c r="C9" s="20">
+        <v>318770</v>
+      </c>
+      <c r="D9" s="20">
+        <v>17364</v>
+      </c>
+      <c r="E9" s="20">
+        <v>2768</v>
+      </c>
+      <c r="F9" s="20">
+        <v>583252</v>
+      </c>
+      <c r="G9" s="21">
+        <v>42537</v>
+      </c>
+      <c r="H9" s="22">
+        <v>71263</v>
+      </c>
+      <c r="I9" s="22">
+        <v>299731</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="136">
+        <v>964691</v>
+      </c>
+      <c r="C10" s="20">
+        <v>331925</v>
+      </c>
+      <c r="D10" s="20">
+        <v>17687</v>
+      </c>
+      <c r="E10" s="20">
+        <v>2976</v>
+      </c>
+      <c r="F10" s="20">
+        <v>590659</v>
+      </c>
+      <c r="G10" s="21">
+        <v>21444</v>
+      </c>
+      <c r="H10" s="22">
+        <v>71399</v>
+      </c>
+      <c r="I10" s="22">
+        <v>311068</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="136">
+        <v>768561</v>
+      </c>
+      <c r="C11" s="20">
+        <v>298160</v>
+      </c>
+      <c r="D11" s="20">
+        <v>7573</v>
+      </c>
+      <c r="E11" s="20">
+        <v>1126</v>
+      </c>
+      <c r="F11" s="20">
+        <v>443292</v>
+      </c>
+      <c r="G11" s="21">
+        <v>18410</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="136">
+        <v>768559</v>
+      </c>
+      <c r="C12" s="20">
+        <v>301429</v>
+      </c>
+      <c r="D12" s="20">
+        <v>7517</v>
+      </c>
+      <c r="E12" s="20">
+        <v>1216</v>
+      </c>
+      <c r="F12" s="24">
+        <v>446297</v>
+      </c>
+      <c r="G12" s="24">
+        <v>12100</v>
+      </c>
+      <c r="H12" s="22">
+        <v>23276</v>
+      </c>
+      <c r="I12" s="22">
+        <v>283371</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="25">
+        <v>768561</v>
+      </c>
+      <c r="C13" s="24">
+        <v>297655</v>
+      </c>
+      <c r="D13" s="24">
+        <v>7938</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="22">
+        <v>24821</v>
+      </c>
+      <c r="I13" s="22">
+        <v>281621</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="136">
+        <v>632772</v>
+      </c>
+      <c r="C14" s="20">
+        <v>202230</v>
+      </c>
+      <c r="D14" s="20">
+        <v>4943</v>
+      </c>
+      <c r="E14" s="20">
+        <v>472</v>
+      </c>
+      <c r="F14" s="20">
+        <v>413125</v>
+      </c>
+      <c r="G14" s="21">
+        <v>12002</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+      <c r="A16" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="136"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="57">
+        <v>100</v>
+      </c>
+      <c r="C17" s="36">
+        <v>33.351951627326123</v>
+      </c>
+      <c r="D17" s="36">
+        <v>2.4539152106649436</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0.46010346237104421</v>
+      </c>
+      <c r="F17" s="36">
+        <v>61.831625052222961</v>
+      </c>
+      <c r="G17" s="36">
+        <v>1.9024046474149297</v>
+      </c>
+      <c r="H17" s="36">
+        <v>7.3441499906607755</v>
+      </c>
+      <c r="I17" s="36">
+        <v>31.36932890223952</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="57">
+        <v>100</v>
+      </c>
+      <c r="C18" s="36">
+        <v>33.410964701338806</v>
+      </c>
+      <c r="D18" s="36">
+        <v>2.4064520960920532</v>
+      </c>
+      <c r="E18" s="36">
+        <v>0.50494978925835721</v>
+      </c>
+      <c r="F18" s="36">
+        <v>61.93584538935545</v>
+      </c>
+      <c r="G18" s="36">
+        <v>1.7417880239553378</v>
+      </c>
+      <c r="H18" s="36">
+        <v>7.1052102047501009</v>
+      </c>
+      <c r="I18" s="36">
+        <v>31.383766351539254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="57">
+        <v>100</v>
+      </c>
+      <c r="C19" s="36">
+        <v>33.04374146747508</v>
+      </c>
+      <c r="D19" s="36">
+        <v>1.799954596860549</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0.28693125570778621</v>
+      </c>
+      <c r="F19" s="36">
+        <v>60.45998148629976</v>
+      </c>
+      <c r="G19" s="36">
+        <v>4.4093911936568286</v>
+      </c>
+      <c r="H19" s="36">
+        <v>7.3871322527109724</v>
+      </c>
+      <c r="I19" s="36">
+        <v>31.070156143262455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="57">
+        <v>100</v>
+      </c>
+      <c r="C20" s="36">
+        <v>34.407390553037196</v>
+      </c>
+      <c r="D20" s="36">
+        <v>1.833436820702173</v>
+      </c>
+      <c r="E20" s="36">
+        <v>0.30849256394016322</v>
+      </c>
+      <c r="F20" s="36">
+        <v>61.227792111670986</v>
+      </c>
+      <c r="G20" s="36">
+        <v>2.2228879506494827</v>
+      </c>
+      <c r="H20" s="36">
+        <v>7.4012300311706021</v>
+      </c>
+      <c r="I20" s="36">
+        <v>32.245351102062727</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="57">
+        <v>100</v>
+      </c>
+      <c r="C21" s="36">
+        <v>38.794578439447221</v>
+      </c>
+      <c r="D21" s="36">
+        <v>0.98534794245349422</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0.14650756413609331</v>
+      </c>
+      <c r="F21" s="36">
+        <v>57.67818039166702</v>
+      </c>
+      <c r="G21" s="36">
+        <v>2.3953856622961611</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="57">
+        <v>100</v>
+      </c>
+      <c r="C22" s="36">
+        <v>39.220020844203241</v>
+      </c>
+      <c r="D22" s="36">
+        <v>0.97806414341644554</v>
+      </c>
+      <c r="E22" s="36">
+        <v>0.15821817192954607</v>
+      </c>
+      <c r="F22" s="36">
+        <v>58.069321938849193</v>
+      </c>
+      <c r="G22" s="36">
+        <v>1.5743749016015687</v>
+      </c>
+      <c r="H22" s="36">
+        <v>3.0285248107171996</v>
+      </c>
+      <c r="I22" s="36">
+        <v>36.870428945598185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="57">
+        <v>100</v>
+      </c>
+      <c r="C23" s="36">
+        <v>38.728871228178377</v>
+      </c>
+      <c r="D23" s="36">
+        <v>1.0328392931725654</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="36">
+        <v>3.229541962186476</v>
+      </c>
+      <c r="I23" s="36">
+        <v>36.642730096193006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="135">
+        <v>100</v>
+      </c>
+      <c r="C24" s="44">
+        <v>31.959378733572279</v>
+      </c>
+      <c r="D24" s="44">
+        <v>0.7811660440095326</v>
+      </c>
+      <c r="E24" s="44">
+        <v>7.4592428236394781E-2</v>
+      </c>
+      <c r="F24" s="44">
+        <v>65.288129057543628</v>
+      </c>
+      <c r="G24" s="44">
+        <v>1.8967337366381571</v>
+      </c>
+      <c r="H24" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="134" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+    </row>
+    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="132"/>
+      <c r="C29" s="130">
+        <v>1950</v>
+      </c>
+      <c r="D29" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="131" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="131" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="131" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" s="130">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="129"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="88">
+        <v>499794</v>
+      </c>
+      <c r="D31" s="88">
+        <v>423330</v>
+      </c>
+      <c r="E31" s="88">
+        <v>368336</v>
+      </c>
+      <c r="F31" s="88">
+        <v>255912</v>
+      </c>
+      <c r="G31" s="88">
+        <v>191909</v>
+      </c>
+      <c r="H31" s="88">
+        <v>154001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="88">
+        <v>114793</v>
+      </c>
+      <c r="D33" s="88">
+        <v>103791</v>
+      </c>
+      <c r="E33" s="88">
+        <v>80373</v>
+      </c>
+      <c r="F33" s="88">
+        <v>57742</v>
+      </c>
+      <c r="G33" s="88">
+        <v>44048</v>
+      </c>
+      <c r="H33" s="88">
+        <v>28819</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="88">
+        <v>27588</v>
+      </c>
+      <c r="F34" s="88">
+        <v>27002</v>
+      </c>
+      <c r="G34" s="88">
+        <v>22301</v>
+      </c>
+      <c r="H34" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="18"/>
+      <c r="C35" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="88">
+        <v>6671</v>
+      </c>
+      <c r="F35" s="88">
+        <v>5602</v>
+      </c>
+      <c r="G35" s="88">
+        <v>4890</v>
+      </c>
+      <c r="H35" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="88">
+        <v>1219</v>
+      </c>
+      <c r="F36" s="88">
+        <v>2430</v>
+      </c>
+      <c r="G36" s="88">
+        <v>1990</v>
+      </c>
+      <c r="H36" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="88">
+        <v>44895</v>
+      </c>
+      <c r="F37" s="88">
+        <v>19708</v>
+      </c>
+      <c r="G37" s="88">
+        <v>14867</v>
+      </c>
+      <c r="H37" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="88">
+        <v>2651</v>
+      </c>
+      <c r="D38" s="88">
+        <v>255</v>
+      </c>
+      <c r="E38" s="88">
+        <v>563</v>
+      </c>
+      <c r="F38" s="88">
+        <v>348</v>
+      </c>
+      <c r="G38" s="88">
+        <v>695</v>
+      </c>
+      <c r="H38" s="88">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="88">
+        <v>364148</v>
+      </c>
+      <c r="D40" s="88">
+        <v>310409</v>
+      </c>
+      <c r="E40" s="88">
+        <v>287183</v>
+      </c>
+      <c r="F40" s="88">
+        <v>200512</v>
+      </c>
+      <c r="G40" s="88">
+        <v>146790</v>
+      </c>
+      <c r="H40" s="88">
+        <v>124534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="88">
+        <v>184611</v>
+      </c>
+      <c r="D41" s="88">
+        <v>157905</v>
+      </c>
+      <c r="E41" s="88">
+        <v>139631</v>
+      </c>
+      <c r="F41" s="88">
+        <v>109274</v>
+      </c>
+      <c r="G41" s="88">
+        <v>79675</v>
+      </c>
+      <c r="H41" s="88">
+        <v>61111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="88">
+        <v>4090</v>
+      </c>
+      <c r="D42" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="88">
+        <v>32376</v>
+      </c>
+      <c r="D43" s="88">
+        <v>28774</v>
+      </c>
+      <c r="E43" s="88">
+        <v>27179</v>
+      </c>
+      <c r="F43" s="88">
+        <v>23507</v>
+      </c>
+      <c r="G43" s="88">
+        <v>21674</v>
+      </c>
+      <c r="H43" s="88">
+        <v>25767</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="88">
+        <v>2875</v>
+      </c>
+      <c r="D44" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="88">
+        <v>61071</v>
+      </c>
+      <c r="D45" s="88">
+        <v>52569</v>
+      </c>
+      <c r="E45" s="88">
+        <v>63052</v>
+      </c>
+      <c r="F45" s="88">
+        <v>21031</v>
+      </c>
+      <c r="G45" s="88">
+        <v>2361</v>
+      </c>
+      <c r="H45" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="88">
+        <v>7680</v>
+      </c>
+      <c r="D46" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="18"/>
+      <c r="C47" s="88">
+        <v>7030</v>
+      </c>
+      <c r="D47" s="88">
+        <v>6851</v>
+      </c>
+      <c r="E47" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="88">
+        <v>4950</v>
+      </c>
+      <c r="G47" s="88">
+        <v>4533</v>
+      </c>
+      <c r="H47" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="88">
+        <v>86091</v>
+      </c>
+      <c r="D48" s="88">
+        <v>64310</v>
+      </c>
+      <c r="E48" s="88">
+        <v>50860</v>
+      </c>
+      <c r="F48" s="88">
+        <v>41750</v>
+      </c>
+      <c r="G48" s="88">
+        <v>38547</v>
+      </c>
+      <c r="H48" s="88">
+        <v>37656</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="18"/>
+      <c r="C49" s="88">
+        <v>12206</v>
+      </c>
+      <c r="D49" s="88">
+        <v>14375</v>
+      </c>
+      <c r="E49" s="88">
+        <v>22636</v>
+      </c>
+      <c r="F49" s="88">
+        <v>23723</v>
+      </c>
+      <c r="G49" s="88">
+        <v>26041</v>
+      </c>
+      <c r="H49" s="88">
+        <v>29799</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="88">
+        <v>73885</v>
+      </c>
+      <c r="D50" s="88">
+        <v>49935</v>
+      </c>
+      <c r="E50" s="88">
+        <v>28224</v>
+      </c>
+      <c r="F50" s="88">
+        <v>18027</v>
+      </c>
+      <c r="G50" s="88">
+        <v>12506</v>
+      </c>
+      <c r="H50" s="88">
+        <v>7857</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="88">
+        <v>15632</v>
+      </c>
+      <c r="F51" s="88">
+        <v>11072</v>
+      </c>
+      <c r="G51" s="88">
+        <v>8772</v>
+      </c>
+      <c r="H51" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="88">
+        <v>12592</v>
+      </c>
+      <c r="F52" s="88">
+        <v>6955</v>
+      </c>
+      <c r="G52" s="88">
+        <v>3734</v>
+      </c>
+      <c r="H52" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="88">
+        <v>9551</v>
+      </c>
+      <c r="D53" s="88">
+        <v>8296</v>
+      </c>
+      <c r="E53" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" s="88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="127"/>
+      <c r="C54" s="10">
+        <v>1620</v>
+      </c>
+      <c r="D54" s="10">
+        <v>579</v>
+      </c>
+      <c r="E54" s="10">
+        <v>217</v>
+      </c>
+      <c r="F54" s="10">
+        <v>310</v>
+      </c>
+      <c r="G54" s="10">
+        <v>376</v>
+      </c>
+      <c r="H54" s="10">
+        <v>415</v>
+      </c>
+      <c r="I54" s="19"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="83"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+    </row>
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
+  <pageSetup scale="73" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBF5D1B-7E84-4227-A958-2479EFE6D553}">
   <dimension ref="A1:I53"/>
